--- a/temple.xlsx
+++ b/temple.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaish_mac/Desktop/DRHS/for github/mapu2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\林芷葳\Documents\GitHub\mapu2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6E6A6FA-E6C8-AA44-A565-C9CB25E9AB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF6D591-6369-48A8-995F-9FD8DA901D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="神社資料" sheetId="1" r:id="rId1"/>
@@ -881,18 +881,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" customWidth="1"/>
-    <col min="2" max="4" width="12.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" customWidth="1"/>
-    <col min="6" max="6" width="11.3984375" customWidth="1"/>
-    <col min="7" max="7" width="12.796875" customWidth="1"/>
-    <col min="8" max="8" width="14.59765625" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="10.375" customWidth="1"/>
+    <col min="6" max="6" width="11.375" customWidth="1"/>
+    <col min="7" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="17.399999999999999">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -950,7 +950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.25" customHeight="1">
+    <row r="3" spans="1:9" ht="16.2" customHeight="1">
       <c r="A3" s="3">
         <v>102</v>
       </c>
@@ -979,7 +979,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.25" customHeight="1">
+    <row r="4" spans="1:9" ht="16.2" customHeight="1">
       <c r="A4" s="3">
         <v>103</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.25" customHeight="1">
+    <row r="5" spans="1:9" ht="16.2" customHeight="1">
       <c r="A5" s="3">
         <v>104</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.25" customHeight="1">
+    <row r="6" spans="1:9" ht="16.2" customHeight="1">
       <c r="A6" s="3">
         <v>105</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.25" customHeight="1">
+    <row r="7" spans="1:9" ht="16.2" customHeight="1">
       <c r="A7" s="3">
         <v>106</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.25" customHeight="1">
+    <row r="8" spans="1:9" ht="16.2" customHeight="1">
       <c r="A8" s="3">
         <v>107</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.25" customHeight="1">
+    <row r="9" spans="1:9" ht="16.2" customHeight="1">
       <c r="A9" s="3">
         <v>108</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.25" customHeight="1">
+    <row r="10" spans="1:9" ht="16.2" customHeight="1">
       <c r="A10" s="3">
         <v>109</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="16.25" customHeight="1">
+    <row r="11" spans="1:9" ht="16.2" customHeight="1">
       <c r="A11" s="3">
         <v>110</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.25" customHeight="1">
+    <row r="12" spans="1:9" ht="16.2" customHeight="1">
       <c r="A12" s="3">
         <v>111</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16.25" customHeight="1">
+    <row r="13" spans="1:9" ht="16.2" customHeight="1">
       <c r="A13" s="3">
         <v>112</v>
       </c>
@@ -1631,10 +1631,10 @@
         <v>142</v>
       </c>
       <c r="E26" s="4">
-        <v>25.042000000000002</v>
+        <v>25.080774440338601</v>
       </c>
       <c r="F26" s="4">
-        <v>121.312</v>
+        <v>121.518359966549</v>
       </c>
       <c r="G26" s="4">
         <v>1944</v>

--- a/temple.xlsx
+++ b/temple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\林芷葳\Documents\GitHub\mapu2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF6D591-6369-48A8-995F-9FD8DA901D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610730DE-DC66-47C9-8E40-656FC0B7B9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -495,7 +495,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,6 +544,12 @@
       <family val="4"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -565,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -578,6 +584,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -880,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
@@ -1965,6 +1972,13 @@
         <v>138</v>
       </c>
     </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/temple.xlsx
+++ b/temple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\林芷葳\Documents\GitHub\mapu2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610730DE-DC66-47C9-8E40-656FC0B7B9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D50CFE2-042B-4C01-A561-467807E58C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="156">
   <si>
     <t>編號</t>
   </si>
@@ -489,6 +489,17 @@
   </si>
   <si>
     <t>桃園市桃園區成功路三段200號</t>
+  </si>
+  <si>
+    <t>臺灣大學</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>給大家測試用的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北市大安區羅斯福路四段1號</t>
   </si>
 </sst>
 </file>
@@ -545,10 +556,11 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF3A1A10"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1973,11 +1985,33 @@
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="1"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="A38" s="1">
+        <v>313</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" s="8">
+        <v>25.019120000000001</v>
+      </c>
+      <c r="F38" s="8">
+        <v>121.54356</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1928</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1945</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
